--- a/03_Outputs/all/03_DS/ds_idx5_viviendas.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx5_viviendas.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>1.271057599405442</v>
+        <v>1.271057599405441</v>
       </c>
       <c r="D2">
-        <v>0.8342580879270183</v>
+        <v>0.8342580879270195</v>
       </c>
       <c r="E2">
-        <v>-0.2199840286414862</v>
+        <v>-0.2199840286414872</v>
       </c>
       <c r="F2">
-        <v>0.5690628800597479</v>
+        <v>0.5690628800597476</v>
       </c>
       <c r="G2">
-        <v>0.09862108320660211</v>
+        <v>0.09862108320660204</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.3393206535214743</v>
+        <v>-0.3393206535214801</v>
       </c>
       <c r="D3">
-        <v>1.173734303031403</v>
+        <v>1.173734303031407</v>
       </c>
       <c r="E3">
-        <v>-1.296284457780534</v>
+        <v>-1.296284457780544</v>
       </c>
       <c r="F3">
-        <v>3.243061037631097</v>
+        <v>3.243061037631096</v>
       </c>
       <c r="G3">
-        <v>-0.6860482966432159</v>
+        <v>-0.6860482966432168</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.4153103868701081</v>
+        <v>0.4153103868701087</v>
       </c>
       <c r="D4">
-        <v>-0.1735150881483148</v>
+        <v>-0.1735150881483147</v>
       </c>
       <c r="E4">
-        <v>-0.2165556033613137</v>
+        <v>-0.2165556033613116</v>
       </c>
       <c r="F4">
-        <v>-0.7192389109698865</v>
+        <v>-0.7192389109698872</v>
       </c>
       <c r="G4">
-        <v>0.127480690586431</v>
+        <v>0.1274806905864309</v>
       </c>
     </row>
     <row r="5">
@@ -487,16 +487,16 @@
         <v>1.305780538818751</v>
       </c>
       <c r="D5">
-        <v>0.187366822353249</v>
+        <v>0.1873668223532491</v>
       </c>
       <c r="E5">
-        <v>0.3881031321342885</v>
+        <v>0.3881031321342879</v>
       </c>
       <c r="F5">
-        <v>0.1351566826008184</v>
+        <v>0.1351566826008194</v>
       </c>
       <c r="G5">
-        <v>0.3458401205127415</v>
+        <v>0.345840120512741</v>
       </c>
     </row>
     <row r="6">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.6343499984795579</v>
+        <v>0.6343499984795551</v>
       </c>
       <c r="D6">
-        <v>0.9252496032258811</v>
+        <v>0.9252496032258832</v>
       </c>
       <c r="E6">
-        <v>-0.5373480508361864</v>
+        <v>-0.5373480508361912</v>
       </c>
       <c r="F6">
-        <v>1.801994305490866</v>
+        <v>1.801994305490865</v>
       </c>
       <c r="G6">
-        <v>-0.06520963118241389</v>
+        <v>-0.06520963118241441</v>
       </c>
     </row>
     <row r="7">
@@ -538,19 +538,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.01513681235362918</v>
+        <v>0.01513681235362982</v>
       </c>
       <c r="D7">
-        <v>-0.2280571249096416</v>
+        <v>-0.2280571249096418</v>
       </c>
       <c r="E7">
-        <v>-0.0715082360112874</v>
+        <v>-0.07150823601128486</v>
       </c>
       <c r="F7">
-        <v>-0.8481840786005369</v>
+        <v>-0.8481840786005375</v>
       </c>
       <c r="G7">
-        <v>-0.05516942855499559</v>
+        <v>-0.05516942855499576</v>
       </c>
     </row>
     <row r="8">
@@ -568,16 +568,16 @@
         <v>1.390647164729408</v>
       </c>
       <c r="D8">
-        <v>0.1641495164280328</v>
+        <v>0.1641495164280329</v>
       </c>
       <c r="E8">
-        <v>0.638834628906476</v>
+        <v>0.6388346289064757</v>
       </c>
       <c r="F8">
-        <v>0.08436776831093099</v>
+        <v>0.08436776831093251</v>
       </c>
       <c r="G8">
-        <v>-0.2410241916033481</v>
+        <v>-0.2410241916033487</v>
       </c>
     </row>
     <row r="9">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.3635767573775878</v>
+        <v>0.3635767573775885</v>
       </c>
       <c r="D9">
-        <v>0.009267328368564719</v>
+        <v>0.009267328368564608</v>
       </c>
       <c r="E9">
-        <v>0.2111021096707576</v>
+        <v>0.2111021096707599</v>
       </c>
       <c r="F9">
-        <v>-0.6232752692261117</v>
+        <v>-0.6232752692261115</v>
       </c>
       <c r="G9">
-        <v>-0.07912804408433503</v>
+        <v>-0.07912804408433519</v>
       </c>
     </row>
     <row r="10">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.4369417642904829</v>
+        <v>-0.4369417642904837</v>
       </c>
       <c r="D10">
-        <v>-0.4859758062316566</v>
+        <v>-0.4859758062316554</v>
       </c>
       <c r="E10">
-        <v>-0.381419607469849</v>
+        <v>-0.3814196074698515</v>
       </c>
       <c r="F10">
-        <v>0.5421189587951689</v>
+        <v>0.5421189587951681</v>
       </c>
       <c r="G10">
-        <v>-0.7654589143960009</v>
+        <v>-0.7654589143960017</v>
       </c>
     </row>
     <row r="11">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>-0.7083627696446108</v>
+        <v>-0.7083627696446074</v>
       </c>
       <c r="D11">
-        <v>-2.306522588829291</v>
+        <v>-2.306522588829294</v>
       </c>
       <c r="E11">
-        <v>0.9519839136657924</v>
+        <v>0.9519839136657904</v>
       </c>
       <c r="F11">
-        <v>-0.1041118728328998</v>
+        <v>-0.1041118728328971</v>
       </c>
       <c r="G11">
-        <v>0.9265412725155454</v>
+        <v>0.9265412725155432</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.1546006707038878</v>
+        <v>0.1546006707038868</v>
       </c>
       <c r="D12">
-        <v>0.3453204246050779</v>
+        <v>0.3453204246050783</v>
       </c>
       <c r="E12">
-        <v>-0.1569343323007328</v>
+        <v>-0.1569343323007329</v>
       </c>
       <c r="F12">
-        <v>0.1565684205077993</v>
+        <v>0.1565684205077988</v>
       </c>
       <c r="G12">
-        <v>0.1240492901369109</v>
+        <v>0.1240492901369107</v>
       </c>
     </row>
     <row r="13">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.3273021665953116</v>
+        <v>0.3273021665953109</v>
       </c>
       <c r="D13">
-        <v>0.7617513129464999</v>
+        <v>0.761751312946501</v>
       </c>
       <c r="E13">
-        <v>-1.227458389362166</v>
+        <v>-1.22745838936216</v>
       </c>
       <c r="F13">
-        <v>-1.446291116363914</v>
+        <v>-1.446291116363918</v>
       </c>
       <c r="G13">
-        <v>0.1692994690585405</v>
+        <v>0.1692994690585418</v>
       </c>
     </row>
     <row r="14">
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.5145273926881876</v>
+        <v>0.514527392688187</v>
       </c>
       <c r="D14">
-        <v>0.9988033116556545</v>
+        <v>0.9988033116556529</v>
       </c>
       <c r="E14">
-        <v>1.098203737886324</v>
+        <v>1.098203737886325</v>
       </c>
       <c r="F14">
-        <v>0.02796189306952149</v>
+        <v>0.02796189306952346</v>
       </c>
       <c r="G14">
-        <v>-0.03911127083522378</v>
+        <v>-0.03911127083522412</v>
       </c>
     </row>
     <row r="15">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>-4.459597070995445</v>
+        <v>-4.459597070995448</v>
       </c>
       <c r="D15">
-        <v>3.634362575888187</v>
+        <v>3.634362575888183</v>
       </c>
       <c r="E15">
-        <v>1.382902384532521</v>
+        <v>1.382902384532537</v>
       </c>
       <c r="F15">
-        <v>-2.571820382253023</v>
+        <v>-2.571820382253024</v>
       </c>
       <c r="G15">
-        <v>-0.3643840570162523</v>
+        <v>-0.3643840570162495</v>
       </c>
     </row>
     <row r="16">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.2016336638482568</v>
+        <v>-0.2016336638482537</v>
       </c>
       <c r="D16">
-        <v>-2.042557556904873</v>
+        <v>-2.042557556904875</v>
       </c>
       <c r="E16">
-        <v>1.035440425859185</v>
+        <v>1.035440425859183</v>
       </c>
       <c r="F16">
-        <v>-0.1168051271406953</v>
+        <v>-0.1168051271406926</v>
       </c>
       <c r="G16">
-        <v>0.01067635646716551</v>
+        <v>0.01067635646716322</v>
       </c>
     </row>
     <row r="17">
@@ -811,16 +811,16 @@
         <v>1.010798813655072</v>
       </c>
       <c r="D17">
-        <v>0.5973650900568793</v>
+        <v>0.5973650900568801</v>
       </c>
       <c r="E17">
-        <v>-0.2360396566563904</v>
+        <v>-0.2360396566563875</v>
       </c>
       <c r="F17">
-        <v>-0.6234417648663145</v>
+        <v>-0.6234417648663155</v>
       </c>
       <c r="G17">
-        <v>-0.03817352917388583</v>
+        <v>-0.03817352917388542</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.931701030728279</v>
+        <v>0.9317010307282797</v>
       </c>
       <c r="D18">
-        <v>-0.1232656523441844</v>
+        <v>-0.1232656523441838</v>
       </c>
       <c r="E18">
-        <v>-0.1559876493633309</v>
+        <v>-0.1559876493633297</v>
       </c>
       <c r="F18">
-        <v>-0.509059238094693</v>
+        <v>-0.5090592380946934</v>
       </c>
       <c r="G18">
-        <v>-0.07073329065512134</v>
+        <v>-0.07073329065512154</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>1.017087707901185</v>
+        <v>1.017087707901186</v>
       </c>
       <c r="D19">
-        <v>-0.371448167877426</v>
+        <v>-0.3714481678774265</v>
       </c>
       <c r="E19">
-        <v>0.1027501931658187</v>
+        <v>0.1027501931658173</v>
       </c>
       <c r="F19">
-        <v>0.1621749029023049</v>
+        <v>0.1621749029023054</v>
       </c>
       <c r="G19">
-        <v>1.051574605148239</v>
+        <v>1.051574605148238</v>
       </c>
     </row>
     <row r="20">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.06089397217879008</v>
+        <v>0.06089397217878875</v>
       </c>
       <c r="D20">
-        <v>0.4625293806290736</v>
+        <v>0.4625293806290757</v>
       </c>
       <c r="E20">
-        <v>-1.272481621011746</v>
+        <v>-1.272481621011743</v>
       </c>
       <c r="F20">
-        <v>-0.6131802984186292</v>
+        <v>-0.6131802984186328</v>
       </c>
       <c r="G20">
-        <v>-0.4791945365181651</v>
+        <v>-0.4791945365181642</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.7463368245696393</v>
+        <v>0.7463368245696412</v>
       </c>
       <c r="D21">
-        <v>-1.186949642604106</v>
+        <v>-1.186949642604107</v>
       </c>
       <c r="E21">
-        <v>0.3921497809193209</v>
+        <v>0.3921497809193188</v>
       </c>
       <c r="F21">
-        <v>0.05761406158163155</v>
+        <v>0.05761406158163296</v>
       </c>
       <c r="G21">
-        <v>0.4481870412525594</v>
+        <v>0.4481870412525578</v>
       </c>
     </row>
     <row r="22">
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>-1.076298197950679</v>
+        <v>-1.076298197950677</v>
       </c>
       <c r="D22">
         <v>-2.281002781470955</v>
       </c>
       <c r="E22">
-        <v>-0.3313040731080406</v>
+        <v>-0.3313040731080404</v>
       </c>
       <c r="F22">
-        <v>-0.7670569806477731</v>
+        <v>-0.7670569806477739</v>
       </c>
       <c r="G22">
-        <v>-0.7433478662768472</v>
+        <v>-0.743347866276849</v>
       </c>
     </row>
     <row r="23">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>1.002613686361428</v>
+        <v>1.002613686361427</v>
       </c>
       <c r="D23">
-        <v>0.7836193482967481</v>
+        <v>0.7836193482967495</v>
       </c>
       <c r="E23">
-        <v>-0.695404226324103</v>
+        <v>-0.6954042263241033</v>
       </c>
       <c r="F23">
-        <v>0.2782292768607526</v>
+        <v>0.2782292768607511</v>
       </c>
       <c r="G23">
-        <v>0.2251396630275192</v>
+        <v>0.2251396630275195</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>-2.512124213654947</v>
+        <v>-2.512124213654948</v>
       </c>
       <c r="D24">
-        <v>-2.687260118721166</v>
+        <v>-2.687260118721165</v>
       </c>
       <c r="E24">
-        <v>-0.8147881425492474</v>
+        <v>-0.8147881425492591</v>
       </c>
       <c r="F24">
         <v>2.820672862552207</v>
       </c>
       <c r="G24">
-        <v>-0.1040520633018379</v>
+        <v>-0.1040520633018418</v>
       </c>
     </row>
     <row r="25">
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="C25">
-        <v>-0.5819898108463347</v>
+        <v>-0.5819898108463336</v>
       </c>
       <c r="D25">
-        <v>-0.9976415007107005</v>
+        <v>-0.9976415007107006</v>
       </c>
       <c r="E25">
-        <v>-1.345297217870132</v>
+        <v>-1.345297217870128</v>
       </c>
       <c r="F25">
-        <v>-1.440970585798009</v>
+        <v>-1.440970585798013</v>
       </c>
       <c r="G25">
         <v>1.163555120506618</v>
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>-1.859794812682709</v>
+        <v>-1.85979481268271</v>
       </c>
       <c r="D26">
-        <v>0.335978547190852</v>
+        <v>0.3359785471908505</v>
       </c>
       <c r="E26">
-        <v>0.07271643731427777</v>
+        <v>0.07271643731427896</v>
       </c>
       <c r="F26">
-        <v>0.4277898867343397</v>
+        <v>0.4277898867343395</v>
       </c>
       <c r="G26">
-        <v>1.408471489737755</v>
+        <v>1.408471489737754</v>
       </c>
     </row>
     <row r="27">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>0.5857843771169974</v>
+        <v>0.5857843771169989</v>
       </c>
       <c r="D27">
-        <v>-0.6847976402353696</v>
+        <v>-0.6847976402353705</v>
       </c>
       <c r="E27">
-        <v>0.8937398212786978</v>
+        <v>0.8937398212786967</v>
       </c>
       <c r="F27">
-        <v>-0.01811210176417307</v>
+        <v>-0.01811210176417094</v>
       </c>
       <c r="G27">
-        <v>-0.2287059015149547</v>
+        <v>-0.2287059015149559</v>
       </c>
     </row>
     <row r="28">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>0.9362150431033543</v>
+        <v>0.9362150431033551</v>
       </c>
       <c r="D28">
-        <v>-0.02910895228342066</v>
+        <v>-0.0291089522834202</v>
       </c>
       <c r="E28">
-        <v>0.1639078429271328</v>
+        <v>0.1639078429271342</v>
       </c>
       <c r="F28">
-        <v>-0.4581412384765298</v>
+        <v>-0.4581412384765296</v>
       </c>
       <c r="G28">
-        <v>-0.3745075128836484</v>
+        <v>-0.3745075128836485</v>
       </c>
     </row>
     <row r="29">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>-1.796599089784601</v>
+        <v>-1.796599089784602</v>
       </c>
       <c r="D29">
-        <v>-2.165037142581709</v>
+        <v>-2.165037142581707</v>
       </c>
       <c r="E29">
-        <v>-1.904611094602231</v>
+        <v>-1.904611094602234</v>
       </c>
       <c r="F29">
-        <v>0.1186789481497578</v>
+        <v>0.1186789481497537</v>
       </c>
       <c r="G29">
-        <v>-0.4727186423569969</v>
+        <v>-0.4727186423569983</v>
       </c>
     </row>
     <row r="30">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.1107170315719937</v>
+        <v>0.110717031571996</v>
       </c>
       <c r="D30">
-        <v>-1.352456914694403</v>
+        <v>-1.352456914694404</v>
       </c>
       <c r="E30">
-        <v>0.8797401082167308</v>
+        <v>0.8797401082167293</v>
       </c>
       <c r="F30">
-        <v>-0.04560345418464964</v>
+        <v>-0.04560345418464734</v>
       </c>
       <c r="G30">
-        <v>0.2608737361508227</v>
+        <v>0.2608737361508209</v>
       </c>
     </row>
     <row r="31">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>-0.3952140675170325</v>
+        <v>-0.3952140675170309</v>
       </c>
       <c r="D31">
-        <v>-0.736941633896087</v>
+        <v>-0.7369416338960875</v>
       </c>
       <c r="E31">
-        <v>0.3534091859632525</v>
+        <v>0.3534091859632555</v>
       </c>
       <c r="F31">
         <v>-1.107714196978097</v>
       </c>
       <c r="G31">
-        <v>-0.9401669214757602</v>
+        <v>-0.9401669214757603</v>
       </c>
     </row>
     <row r="32">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>0.3193989540469084</v>
+        <v>0.3193989540469067</v>
       </c>
       <c r="D32">
-        <v>0.8512790572696529</v>
+        <v>0.8512790572696542</v>
       </c>
       <c r="E32">
-        <v>-0.8934955120680294</v>
+        <v>-0.8934955120680286</v>
       </c>
       <c r="F32">
-        <v>0.1047433236289026</v>
+        <v>0.1047433236289002</v>
       </c>
       <c r="G32">
-        <v>0.2535865323474311</v>
+        <v>0.2535865323474315</v>
       </c>
     </row>
     <row r="33">
@@ -1243,16 +1243,16 @@
         <v>0.1049444776534907</v>
       </c>
       <c r="D33">
-        <v>0.3282609478943284</v>
+        <v>0.3282609478943276</v>
       </c>
       <c r="E33">
-        <v>0.3478638975083241</v>
+        <v>0.3478638975083262</v>
       </c>
       <c r="F33">
-        <v>-0.553950475792097</v>
+        <v>-0.5539504757920967</v>
       </c>
       <c r="G33">
-        <v>-0.02992095845562336</v>
+        <v>-0.02992095845562345</v>
       </c>
     </row>
     <row r="34">
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="C34">
-        <v>0.9817339683688542</v>
+        <v>0.9817339683688538</v>
       </c>
       <c r="D34">
-        <v>0.7122117626327821</v>
+        <v>0.7122117626327834</v>
       </c>
       <c r="E34">
-        <v>-0.9670294446634468</v>
+        <v>-0.9670294446634426</v>
       </c>
       <c r="F34">
-        <v>-1.048918715770857</v>
+        <v>-1.04891871577086</v>
       </c>
       <c r="G34">
-        <v>-0.009155645977410634</v>
+        <v>-0.009155645977409588</v>
       </c>
     </row>
     <row r="35">
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="C35">
-        <v>0.9689952816135117</v>
+        <v>0.9689952816135088</v>
       </c>
       <c r="D35">
-        <v>0.9171584581924233</v>
+        <v>0.9171584581924257</v>
       </c>
       <c r="E35">
-        <v>-0.6290109442339012</v>
+        <v>-0.6290109442339058</v>
       </c>
       <c r="F35">
-        <v>1.695432626923701</v>
+        <v>1.6954326269237</v>
       </c>
       <c r="G35">
-        <v>-0.11330286403057</v>
+        <v>-0.1133028640305705</v>
       </c>
     </row>
     <row r="36">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.29164198558592</v>
+        <v>-0.2916419855859193</v>
       </c>
       <c r="D36">
-        <v>-0.3100404855352656</v>
+        <v>-0.3100404855352661</v>
       </c>
       <c r="E36">
-        <v>0.07339029933689593</v>
+        <v>0.07339029933689889</v>
       </c>
       <c r="F36">
-        <v>-1.004897811339507</v>
+        <v>-1.004897811339508</v>
       </c>
       <c r="G36">
-        <v>-0.3795682343898947</v>
+        <v>-0.379568234389895</v>
       </c>
     </row>
     <row r="37">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="C37">
-        <v>-0.2821789423445243</v>
+        <v>-0.2821789423445239</v>
       </c>
       <c r="D37">
-        <v>-0.8697951969716473</v>
+        <v>-0.869795196971648</v>
       </c>
       <c r="E37">
-        <v>0.6671345849700504</v>
+        <v>0.667134584970047</v>
       </c>
       <c r="F37">
-        <v>0.6057572883375074</v>
+        <v>0.6057572883375093</v>
       </c>
       <c r="G37">
-        <v>-0.4866951038167533</v>
+        <v>-0.4866951038167548</v>
       </c>
     </row>
     <row r="38">
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="C38">
-        <v>0.2727977176939054</v>
+        <v>0.2727977176939069</v>
       </c>
       <c r="D38">
-        <v>-0.5383824255751577</v>
+        <v>-0.5383824255751589</v>
       </c>
       <c r="E38">
         <v>1.207779311929461</v>
       </c>
       <c r="F38">
-        <v>-0.05992182284969707</v>
+        <v>-0.05992182284969433</v>
       </c>
       <c r="G38">
-        <v>-0.1085621039539696</v>
+        <v>-0.1085621039539708</v>
       </c>
     </row>
     <row r="39">
@@ -1405,16 +1405,16 @@
         <v>1.433498542264154</v>
       </c>
       <c r="D39">
-        <v>0.327360227761599</v>
+        <v>0.3273602277615992</v>
       </c>
       <c r="E39">
-        <v>0.3568594361268688</v>
+        <v>0.3568594361268683</v>
       </c>
       <c r="F39">
-        <v>0.1504114962598532</v>
+        <v>0.1504114962598542</v>
       </c>
       <c r="G39">
-        <v>0.3408697696718003</v>
+        <v>0.3408697696717998</v>
       </c>
     </row>
     <row r="40">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C40">
-        <v>1.286559713213187</v>
+        <v>1.286559713213188</v>
       </c>
       <c r="D40">
         <v>-0.04315204750642388</v>
       </c>
       <c r="E40">
-        <v>0.04385686975734911</v>
+        <v>0.04385686975734809</v>
       </c>
       <c r="F40">
-        <v>0.1944957283153274</v>
+        <v>0.1944957283153277</v>
       </c>
       <c r="G40">
-        <v>1.033337392551942</v>
+        <v>1.033337392551941</v>
       </c>
     </row>
     <row r="41">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C41">
-        <v>-0.1364586050668396</v>
+        <v>-0.1364586050668369</v>
       </c>
       <c r="D41">
-        <v>-1.951242305425138</v>
+        <v>-1.951242305425139</v>
       </c>
       <c r="E41">
-        <v>-0.3327460024377482</v>
+        <v>-0.3327460024377485</v>
       </c>
       <c r="F41">
-        <v>-0.7210952173427183</v>
+        <v>-0.7210952173427188</v>
       </c>
       <c r="G41">
-        <v>0.4167467215789957</v>
+        <v>0.4167467215789942</v>
       </c>
     </row>
     <row r="42">
@@ -1483,19 +1483,19 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.5601655501465727</v>
+        <v>0.5601655501465737</v>
       </c>
       <c r="D42">
-        <v>-0.2282597097630167</v>
+        <v>-0.2282597097630157</v>
       </c>
       <c r="E42">
-        <v>-0.2617822490107976</v>
+        <v>-0.2617822490107947</v>
       </c>
       <c r="F42">
-        <v>-1.080155838664481</v>
+        <v>-1.080155838664482</v>
       </c>
       <c r="G42">
-        <v>-0.9659550966538921</v>
+        <v>-0.9659550966538918</v>
       </c>
     </row>
     <row r="43">
@@ -1513,16 +1513,16 @@
         <v>-2.43516099586575</v>
       </c>
       <c r="D43">
-        <v>-0.9279772877158957</v>
+        <v>-0.9279772877158992</v>
       </c>
       <c r="E43">
-        <v>1.850127590066357</v>
+        <v>1.850127590066355</v>
       </c>
       <c r="F43">
-        <v>0.3969036083949445</v>
+        <v>0.3969036083949484</v>
       </c>
       <c r="G43">
-        <v>-0.2946049037028229</v>
+        <v>-0.294604903702825</v>
       </c>
     </row>
     <row r="44">
@@ -1540,16 +1540,16 @@
         <v>1.413900431611162</v>
       </c>
       <c r="D44">
-        <v>0.001936282561996814</v>
+        <v>0.001936282561997064</v>
       </c>
       <c r="E44">
-        <v>0.3949843352153082</v>
+        <v>0.3949843352153073</v>
       </c>
       <c r="F44">
-        <v>0.1241454882220205</v>
+        <v>0.1241454882220215</v>
       </c>
       <c r="G44">
-        <v>0.1471251689930762</v>
+        <v>0.1471251689930755</v>
       </c>
     </row>
     <row r="45">
@@ -1570,13 +1570,13 @@
         <v>0.6681870085393292</v>
       </c>
       <c r="E45">
-        <v>0.2986486335205469</v>
+        <v>0.2986486335205471</v>
       </c>
       <c r="F45">
-        <v>0.1884309708064471</v>
+        <v>0.1884309708064479</v>
       </c>
       <c r="G45">
-        <v>0.7746071246287179</v>
+        <v>0.7746071246287175</v>
       </c>
     </row>
     <row r="46">
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="C46">
-        <v>-2.445110502517237</v>
+        <v>-2.445110502517239</v>
       </c>
       <c r="D46">
-        <v>0.4900661693895101</v>
+        <v>0.4900661693895081</v>
       </c>
       <c r="E46">
-        <v>0.003474443433736752</v>
+        <v>0.003474443433741037</v>
       </c>
       <c r="F46">
-        <v>-0.4568064410907967</v>
+        <v>-0.4568064410907977</v>
       </c>
       <c r="G46">
-        <v>1.347342381135713</v>
+        <v>1.347342381135712</v>
       </c>
     </row>
     <row r="47">
@@ -1621,16 +1621,16 @@
         <v>1.738439092819081</v>
       </c>
       <c r="D47">
-        <v>0.6566238065106713</v>
+        <v>0.6566238065106719</v>
       </c>
       <c r="E47">
-        <v>0.3079112680310632</v>
+        <v>0.307911268031063</v>
       </c>
       <c r="F47">
-        <v>0.179693996447873</v>
+        <v>0.1796939964478739</v>
       </c>
       <c r="G47">
-        <v>0.2349838055561526</v>
+        <v>0.2349838055561524</v>
       </c>
     </row>
     <row r="48">
@@ -1645,19 +1645,19 @@
         </is>
       </c>
       <c r="C48">
-        <v>1.985513320056326</v>
+        <v>1.985513320056325</v>
       </c>
       <c r="D48">
-        <v>1.252183730563764</v>
+        <v>1.252183730563765</v>
       </c>
       <c r="E48">
-        <v>0.4533850004516169</v>
+        <v>0.4533850004516176</v>
       </c>
       <c r="F48">
-        <v>0.1829071580604683</v>
+        <v>0.1829071580604693</v>
       </c>
       <c r="G48">
-        <v>-0.1269116510917501</v>
+        <v>-0.1269116510917499</v>
       </c>
     </row>
     <row r="49">
@@ -1672,19 +1672,19 @@
         </is>
       </c>
       <c r="C49">
-        <v>0.5754397430151627</v>
+        <v>0.5754397430151618</v>
       </c>
       <c r="D49">
-        <v>0.4567179437362044</v>
+        <v>0.4567179437362043</v>
       </c>
       <c r="E49">
-        <v>0.3945472833790161</v>
+        <v>0.3945472833790149</v>
       </c>
       <c r="F49">
-        <v>0.6047996450995803</v>
+        <v>0.6047996450995813</v>
       </c>
       <c r="G49">
-        <v>0.2692383969514764</v>
+        <v>0.2692383969514757</v>
       </c>
     </row>
     <row r="50">
@@ -1699,19 +1699,19 @@
         </is>
       </c>
       <c r="C50">
-        <v>0.3089816956750719</v>
+        <v>0.3089816956750725</v>
       </c>
       <c r="D50">
-        <v>-0.7488968306279472</v>
+        <v>-0.7488968306279468</v>
       </c>
       <c r="E50">
-        <v>0.6462113217586305</v>
+        <v>0.6462113217586269</v>
       </c>
       <c r="F50">
-        <v>0.668206945317482</v>
+        <v>0.6682069453174837</v>
       </c>
       <c r="G50">
-        <v>-1.154565039430363</v>
+        <v>-1.154565039430364</v>
       </c>
     </row>
     <row r="51">
@@ -1726,19 +1726,19 @@
         </is>
       </c>
       <c r="C51">
-        <v>1.026233351126564</v>
+        <v>1.026233351126565</v>
       </c>
       <c r="D51">
-        <v>0.2921665867337575</v>
+        <v>0.2921665867337571</v>
       </c>
       <c r="E51">
         <v>0.3371759233832155</v>
       </c>
       <c r="F51">
-        <v>0.1596972346012543</v>
+        <v>0.1596972346012552</v>
       </c>
       <c r="G51">
-        <v>1.02322058398115</v>
+        <v>1.023220583981149</v>
       </c>
     </row>
     <row r="52">
@@ -1753,19 +1753,19 @@
         </is>
       </c>
       <c r="C52">
-        <v>1.028577996189317</v>
+        <v>1.028577996189318</v>
       </c>
       <c r="D52">
-        <v>0.1605740664580391</v>
+        <v>0.1605740664580399</v>
       </c>
       <c r="E52">
-        <v>0.1110199787153866</v>
+        <v>0.1110199787153884</v>
       </c>
       <c r="F52">
         <v>-0.594249768393895</v>
       </c>
       <c r="G52">
-        <v>-0.7689798084716611</v>
+        <v>-0.768979808471661</v>
       </c>
     </row>
     <row r="53">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="C53">
-        <v>0.5644792937155394</v>
+        <v>0.5644792937155378</v>
       </c>
       <c r="D53">
-        <v>-0.02266903145771585</v>
+        <v>-0.02266903145771416</v>
       </c>
       <c r="E53">
-        <v>-0.4256721537119518</v>
+        <v>-0.425672153711957</v>
       </c>
       <c r="F53">
         <v>1.499875895543421</v>
       </c>
       <c r="G53">
-        <v>-0.1974969660286926</v>
+        <v>-0.1974969660286935</v>
       </c>
     </row>
     <row r="54">
@@ -1807,19 +1807,19 @@
         </is>
       </c>
       <c r="C54">
-        <v>1.131575993023759</v>
+        <v>1.13157599302376</v>
       </c>
       <c r="D54">
-        <v>-0.4292505906291689</v>
+        <v>-0.429250590629169</v>
       </c>
       <c r="E54">
-        <v>0.5819077800581064</v>
+        <v>0.5819077800581054</v>
       </c>
       <c r="F54">
-        <v>0.06289374513134119</v>
+        <v>0.06289374513134272</v>
       </c>
       <c r="G54">
-        <v>-0.05423763757439084</v>
+        <v>-0.05423763757439184</v>
       </c>
     </row>
     <row r="55">
@@ -1834,19 +1834,19 @@
         </is>
       </c>
       <c r="C55">
-        <v>-0.06592921140582132</v>
+        <v>-0.06592921140581981</v>
       </c>
       <c r="D55">
         <v>-1.922886053969074</v>
       </c>
       <c r="E55">
-        <v>0.1637041883476109</v>
+        <v>0.1637041883476059</v>
       </c>
       <c r="F55">
-        <v>0.7166751074427586</v>
+        <v>0.7166751074427598</v>
       </c>
       <c r="G55">
-        <v>-0.09812220528996335</v>
+        <v>-0.09812220528996558</v>
       </c>
     </row>
     <row r="56">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C56">
-        <v>0.9175760391652003</v>
+        <v>0.9175760391651981</v>
       </c>
       <c r="D56">
-        <v>0.7154964008293088</v>
+        <v>0.7154964008293102</v>
       </c>
       <c r="E56">
-        <v>-0.4563439583811857</v>
+        <v>-0.4563439583811892</v>
       </c>
       <c r="F56">
         <v>1.310916292090746</v>
       </c>
       <c r="G56">
-        <v>0.4036656575288431</v>
+        <v>0.4036656575288426</v>
       </c>
     </row>
     <row r="57">
@@ -1888,19 +1888,19 @@
         </is>
       </c>
       <c r="C57">
-        <v>0.7068442195799507</v>
+        <v>0.7068442195799466</v>
       </c>
       <c r="D57">
-        <v>1.56459736493135</v>
+        <v>1.564597364931354</v>
       </c>
       <c r="E57">
-        <v>-1.363613549230529</v>
+        <v>-1.363613549230531</v>
       </c>
       <c r="F57">
-        <v>1.24748972775649</v>
+        <v>1.247489727756487</v>
       </c>
       <c r="G57">
-        <v>-0.6672989969092032</v>
+        <v>-0.6672989969092025</v>
       </c>
     </row>
     <row r="58">
@@ -1915,19 +1915,19 @@
         </is>
       </c>
       <c r="C58">
-        <v>0.8614730730771833</v>
+        <v>0.8614730730771821</v>
       </c>
       <c r="D58">
-        <v>0.4109131244090681</v>
+        <v>0.4109131244090694</v>
       </c>
       <c r="E58">
-        <v>-0.08778671270399011</v>
+        <v>-0.08778671270399341</v>
       </c>
       <c r="F58">
         <v>1.111125447568662</v>
       </c>
       <c r="G58">
-        <v>-0.1668656173939993</v>
+        <v>-0.1668656173939999</v>
       </c>
     </row>
     <row r="59">
@@ -1942,19 +1942,19 @@
         </is>
       </c>
       <c r="C59">
-        <v>0.314867472286296</v>
+        <v>0.314867472286299</v>
       </c>
       <c r="D59">
-        <v>-1.999625369384463</v>
+        <v>-1.999625369384465</v>
       </c>
       <c r="E59">
-        <v>0.8402746688772249</v>
+        <v>0.8402746688772222</v>
       </c>
       <c r="F59">
-        <v>-0.08474573831743024</v>
+        <v>-0.08474573831742782</v>
       </c>
       <c r="G59">
-        <v>-0.425017781245697</v>
+        <v>-0.4250177812456991</v>
       </c>
     </row>
     <row r="60">
@@ -1969,19 +1969,19 @@
         </is>
       </c>
       <c r="C60">
-        <v>1.317042894654736</v>
+        <v>1.317042894654735</v>
       </c>
       <c r="D60">
-        <v>0.9688619358736784</v>
+        <v>0.96886193587368</v>
       </c>
       <c r="E60">
-        <v>-0.4108930403944668</v>
+        <v>-0.4108930403944654</v>
       </c>
       <c r="F60">
-        <v>-0.1694589613264389</v>
+        <v>-0.1694589613264402</v>
       </c>
       <c r="G60">
-        <v>-0.05620129847605018</v>
+        <v>-0.05620129847604961</v>
       </c>
     </row>
     <row r="61">
@@ -1996,19 +1996,19 @@
         </is>
       </c>
       <c r="C61">
-        <v>-0.6825213147984183</v>
+        <v>-0.6825213147984196</v>
       </c>
       <c r="D61">
-        <v>1.005867950749719</v>
+        <v>1.005867950749722</v>
       </c>
       <c r="E61">
-        <v>-2.685109572116178</v>
+        <v>-2.685109572116166</v>
       </c>
       <c r="F61">
-        <v>-3.098947753266879</v>
+        <v>-3.098947753266887</v>
       </c>
       <c r="G61">
-        <v>-0.5680113722832933</v>
+        <v>-0.5680113722832902</v>
       </c>
     </row>
     <row r="62">
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="C62">
-        <v>1.112033229145491</v>
+        <v>1.112033229145492</v>
       </c>
       <c r="D62">
-        <v>-0.1296550814621238</v>
+        <v>-0.1296550814621241</v>
       </c>
       <c r="E62">
-        <v>0.4529063538702637</v>
+        <v>0.4529063538702629</v>
       </c>
       <c r="F62">
-        <v>0.1038744288353043</v>
+        <v>0.1038744288353056</v>
       </c>
       <c r="G62">
-        <v>0.3055796733947459</v>
+        <v>0.3055796733947451</v>
       </c>
     </row>
     <row r="63">
@@ -2053,16 +2053,16 @@
         <v>1.521614083340702</v>
       </c>
       <c r="D63">
-        <v>0.6096018840430427</v>
+        <v>0.6096018840430429</v>
       </c>
       <c r="E63">
-        <v>0.3138552446304769</v>
+        <v>0.3138552446304768</v>
       </c>
       <c r="F63">
-        <v>0.1780869546209765</v>
+        <v>0.1780869546209772</v>
       </c>
       <c r="G63">
-        <v>0.5141003530222281</v>
+        <v>0.5141003530222279</v>
       </c>
     </row>
     <row r="64">
@@ -2077,19 +2077,19 @@
         </is>
       </c>
       <c r="C64">
-        <v>0.9666486091334825</v>
+        <v>0.9666486091334799</v>
       </c>
       <c r="D64">
-        <v>1.186136514150759</v>
+        <v>1.186136514150761</v>
       </c>
       <c r="E64">
-        <v>-1.076527478166029</v>
+        <v>-1.07652747816603</v>
       </c>
       <c r="F64">
-        <v>0.6635531331353782</v>
+        <v>0.6635531331353756</v>
       </c>
       <c r="G64">
-        <v>-0.1175608191020385</v>
+        <v>-0.1175608191020379</v>
       </c>
     </row>
     <row r="65">
@@ -2104,19 +2104,19 @@
         </is>
       </c>
       <c r="C65">
-        <v>1.056217319950795</v>
+        <v>1.056217319950794</v>
       </c>
       <c r="D65">
-        <v>1.105243819089223</v>
+        <v>1.105243819089225</v>
       </c>
       <c r="E65">
-        <v>-0.5496321928348582</v>
+        <v>-0.5496321928348584</v>
       </c>
       <c r="F65">
-        <v>0.4028380977773727</v>
+        <v>0.4028380977773712</v>
       </c>
       <c r="G65">
-        <v>-0.5869420643122426</v>
+        <v>-0.5869420643122419</v>
       </c>
     </row>
     <row r="66">
@@ -2131,19 +2131,19 @@
         </is>
       </c>
       <c r="C66">
-        <v>-1.302355101773535</v>
+        <v>-1.302355101773541</v>
       </c>
       <c r="D66">
-        <v>0.4859029630329855</v>
+        <v>0.4859029630329896</v>
       </c>
       <c r="E66">
-        <v>-2.416463837874833</v>
+        <v>-2.416463837874844</v>
       </c>
       <c r="F66">
-        <v>3.376294968933421</v>
+        <v>3.376294968933418</v>
       </c>
       <c r="G66">
-        <v>-0.02468751631115346</v>
+        <v>-0.02468751631115462</v>
       </c>
     </row>
     <row r="67">
@@ -2158,19 +2158,19 @@
         </is>
       </c>
       <c r="C67">
-        <v>0.9742291411959861</v>
+        <v>0.9742291411959872</v>
       </c>
       <c r="D67">
-        <v>-0.280614077775126</v>
+        <v>-0.2806140777751263</v>
       </c>
       <c r="E67">
-        <v>0.6528642542612084</v>
+        <v>0.6528642542612078</v>
       </c>
       <c r="F67">
-        <v>0.05919378359414999</v>
+        <v>0.05919378359415162</v>
       </c>
       <c r="G67">
-        <v>0.1049185188900401</v>
+        <v>0.1049185188900392</v>
       </c>
     </row>
     <row r="68">
@@ -2185,19 +2185,19 @@
         </is>
       </c>
       <c r="C68">
-        <v>0.3466389857217074</v>
+        <v>0.3466389857217051</v>
       </c>
       <c r="D68">
-        <v>1.351175458616427</v>
+        <v>1.351175458616428</v>
       </c>
       <c r="E68">
-        <v>-0.986277441731921</v>
+        <v>-0.9862774417319183</v>
       </c>
       <c r="F68">
-        <v>-0.1469562041221525</v>
+        <v>-0.1469562041221554</v>
       </c>
       <c r="G68">
-        <v>0.1521490761038595</v>
+        <v>0.1521490761038605</v>
       </c>
     </row>
     <row r="69">
@@ -2212,16 +2212,16 @@
         </is>
       </c>
       <c r="C69">
-        <v>-0.875933536978497</v>
+        <v>-0.8759335369784983</v>
       </c>
       <c r="D69">
-        <v>0.3232047983094823</v>
+        <v>0.3232047983094838</v>
       </c>
       <c r="E69">
-        <v>-0.8906616137990248</v>
+        <v>-0.8906616137990213</v>
       </c>
       <c r="F69">
-        <v>-0.9533286015023371</v>
+        <v>-0.9533286015023401</v>
       </c>
       <c r="G69">
         <v>-1.622220241830757</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="C70">
-        <v>1.657873897479739</v>
+        <v>1.657873897479738</v>
       </c>
       <c r="D70">
-        <v>1.272766350403104</v>
+        <v>1.272766350403106</v>
       </c>
       <c r="E70">
-        <v>-0.2125931611238263</v>
+        <v>-0.2125931611238238</v>
       </c>
       <c r="F70">
-        <v>-0.3913078315030795</v>
+        <v>-0.3913078315030804</v>
       </c>
       <c r="G70">
-        <v>-0.1618897922049723</v>
+        <v>-0.1618897922049714</v>
       </c>
     </row>
     <row r="71">
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="C71">
-        <v>0.7525862975433335</v>
+        <v>0.7525862975433341</v>
       </c>
       <c r="D71">
-        <v>0.190466212373492</v>
+        <v>0.1904662123734923</v>
       </c>
       <c r="E71">
-        <v>-0.1176582328554409</v>
+        <v>-0.1176582328554389</v>
       </c>
       <c r="F71">
-        <v>-0.5582451719531655</v>
+        <v>-0.558245171953166</v>
       </c>
       <c r="G71">
-        <v>0.09616348093155161</v>
+        <v>0.09616348093155164</v>
       </c>
     </row>
     <row r="72">
@@ -2293,16 +2293,16 @@
         </is>
       </c>
       <c r="C72">
-        <v>-5.747871574034112</v>
+        <v>-5.747871574034116</v>
       </c>
       <c r="D72">
-        <v>3.368617975490396</v>
+        <v>3.368617975490388</v>
       </c>
       <c r="E72">
-        <v>4.634478526666387</v>
+        <v>4.634478526666394</v>
       </c>
       <c r="F72">
-        <v>0.4394220268693301</v>
+        <v>0.4394220268693378</v>
       </c>
       <c r="G72">
         <v>-1.00361133701912</v>
@@ -2320,19 +2320,19 @@
         </is>
       </c>
       <c r="C73">
-        <v>-2.190228298036895</v>
+        <v>-2.190228298036899</v>
       </c>
       <c r="D73">
-        <v>2.128924405169712</v>
+        <v>2.128924405169709</v>
       </c>
       <c r="E73">
-        <v>0.6577876466097451</v>
+        <v>0.6577876466097494</v>
       </c>
       <c r="F73">
-        <v>-0.002655251678951042</v>
+        <v>-0.002655251678950865</v>
       </c>
       <c r="G73">
-        <v>0.9063796000590227</v>
+        <v>0.9063796000590231</v>
       </c>
     </row>
     <row r="74">
@@ -2347,19 +2347,19 @@
         </is>
       </c>
       <c r="C74">
-        <v>0.1049950823983272</v>
+        <v>0.1049950823983305</v>
       </c>
       <c r="D74">
-        <v>-2.130043264850464</v>
+        <v>-2.130043264850466</v>
       </c>
       <c r="E74">
-        <v>0.9905426115780032</v>
+        <v>0.9905426115780005</v>
       </c>
       <c r="F74">
-        <v>-0.1221968886423491</v>
+        <v>-0.1221968886423464</v>
       </c>
       <c r="G74">
-        <v>-0.5270870262140295</v>
+        <v>-0.5270870262140316</v>
       </c>
     </row>
     <row r="75">
@@ -2374,19 +2374,19 @@
         </is>
       </c>
       <c r="C75">
-        <v>-0.8023061291679184</v>
+        <v>-0.8023061291679191</v>
       </c>
       <c r="D75">
-        <v>0.8835173552001813</v>
+        <v>0.8835173552001779</v>
       </c>
       <c r="E75">
-        <v>1.096068437215771</v>
+        <v>1.096068437215773</v>
       </c>
       <c r="F75">
-        <v>0.03019202979608907</v>
+        <v>0.03019202979609092</v>
       </c>
       <c r="G75">
-        <v>1.675485355711419</v>
+        <v>1.675485355711418</v>
       </c>
     </row>
     <row r="76">
@@ -2401,19 +2401,19 @@
         </is>
       </c>
       <c r="C76">
-        <v>-6.295672637302488</v>
+        <v>-6.295672637302494</v>
       </c>
       <c r="D76">
-        <v>1.14115596346292</v>
+        <v>1.141155963462922</v>
       </c>
       <c r="E76">
-        <v>-3.043298159082615</v>
+        <v>-3.043298159082609</v>
       </c>
       <c r="F76">
-        <v>0.1020446918927018</v>
+        <v>0.1020446918926927</v>
       </c>
       <c r="G76">
-        <v>0.6950920307865852</v>
+        <v>0.6950920307865862</v>
       </c>
     </row>
     <row r="77">
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="C77">
-        <v>0.09492080097640376</v>
+        <v>0.09492080097640293</v>
       </c>
       <c r="D77">
-        <v>1.283060215210546</v>
+        <v>1.283060215210545</v>
       </c>
       <c r="E77">
-        <v>0.1909821674565524</v>
+        <v>0.1909821674565571</v>
       </c>
       <c r="F77">
-        <v>-0.6304464806631896</v>
+        <v>-0.63044648066319</v>
       </c>
       <c r="G77">
-        <v>0.7682241104692694</v>
+        <v>0.76822411046927</v>
       </c>
     </row>
     <row r="78">
@@ -2458,16 +2458,16 @@
         <v>1.653351756080408</v>
       </c>
       <c r="D78">
-        <v>0.6820819833280886</v>
+        <v>0.682081983328089</v>
       </c>
       <c r="E78">
-        <v>0.7863552254572227</v>
+        <v>0.7863552254572226</v>
       </c>
       <c r="F78">
-        <v>0.07897314324307128</v>
+        <v>0.07897314324307292</v>
       </c>
       <c r="G78">
-        <v>-0.749455208644429</v>
+        <v>-0.7494552086444294</v>
       </c>
     </row>
     <row r="79">
@@ -2482,19 +2482,19 @@
         </is>
       </c>
       <c r="C79">
-        <v>-0.508165540969198</v>
+        <v>-0.5081655409691975</v>
       </c>
       <c r="D79">
-        <v>-0.1107339433539284</v>
+        <v>-0.1107339433539283</v>
       </c>
       <c r="E79">
-        <v>-0.7336251454448871</v>
+        <v>-0.7336251454448819</v>
       </c>
       <c r="F79">
-        <v>-1.47149302296411</v>
+        <v>-1.471493022964113</v>
       </c>
       <c r="G79">
-        <v>0.2877132031876352</v>
+        <v>0.2877132031876357</v>
       </c>
     </row>
     <row r="80">
@@ -2509,19 +2509,19 @@
         </is>
       </c>
       <c r="C80">
-        <v>-0.1507637191680755</v>
+        <v>-0.1507637191680729</v>
       </c>
       <c r="D80">
-        <v>-1.82157944544553</v>
+        <v>-1.821579445445532</v>
       </c>
       <c r="E80">
-        <v>0.4256243964897374</v>
+        <v>0.4256243964897358</v>
       </c>
       <c r="F80">
-        <v>0.03027929219993767</v>
+        <v>0.03027929219993919</v>
       </c>
       <c r="G80">
-        <v>1.544854260593377</v>
+        <v>1.544854260593375</v>
       </c>
     </row>
     <row r="81">
@@ -2536,16 +2536,16 @@
         </is>
       </c>
       <c r="C81">
-        <v>-0.8568665200425881</v>
+        <v>-0.856866520042589</v>
       </c>
       <c r="D81">
-        <v>-0.3689200983826005</v>
+        <v>-0.3689200983825986</v>
       </c>
       <c r="E81">
-        <v>-0.5495427161892218</v>
+        <v>-0.5495427161892217</v>
       </c>
       <c r="F81">
-        <v>-0.2762055826329707</v>
+        <v>-0.2762055826329726</v>
       </c>
       <c r="G81">
         <v>-2.422237343258757</v>
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C82">
-        <v>1.045718204446449</v>
+        <v>1.045718204446447</v>
       </c>
       <c r="D82">
-        <v>1.629732263174547</v>
+        <v>1.629732263174548</v>
       </c>
       <c r="E82">
-        <v>0.1504680064453023</v>
+        <v>0.1504680064453057</v>
       </c>
       <c r="F82">
-        <v>-0.5376149741437893</v>
+        <v>-0.5376149741437899</v>
       </c>
       <c r="G82">
-        <v>-0.5237031829317921</v>
+        <v>-0.5237031829317911</v>
       </c>
     </row>
     <row r="83">
@@ -2590,19 +2590,19 @@
         </is>
       </c>
       <c r="C83">
-        <v>0.1575614640683677</v>
+        <v>0.1575614640683646</v>
       </c>
       <c r="D83">
-        <v>1.142009230895048</v>
+        <v>1.14200923089505</v>
       </c>
       <c r="E83">
-        <v>-0.8567788209474982</v>
+        <v>-0.8567788209474996</v>
       </c>
       <c r="F83">
-        <v>0.7756494545185151</v>
+        <v>0.7756494545185129</v>
       </c>
       <c r="G83">
-        <v>-0.4587946815754302</v>
+        <v>-0.4587946815754299</v>
       </c>
     </row>
     <row r="84">
@@ -2617,19 +2617,19 @@
         </is>
       </c>
       <c r="C84">
-        <v>-0.5978228293680055</v>
+        <v>-0.597822829368004</v>
       </c>
       <c r="D84">
-        <v>-0.6140501644726228</v>
+        <v>-0.6140501644726239</v>
       </c>
       <c r="E84">
-        <v>0.3299535950705912</v>
+        <v>0.3299535950705943</v>
       </c>
       <c r="F84">
-        <v>-0.9737762530620586</v>
+        <v>-0.9737762530620584</v>
       </c>
       <c r="G84">
-        <v>-0.2072895755936061</v>
+        <v>-0.2072895755936066</v>
       </c>
     </row>
     <row r="85">
@@ -2644,19 +2644,19 @@
         </is>
       </c>
       <c r="C85">
-        <v>0.7247548638536331</v>
+        <v>0.7247548638536321</v>
       </c>
       <c r="D85">
-        <v>1.102177202290807</v>
+        <v>1.102177202290809</v>
       </c>
       <c r="E85">
-        <v>-1.081096364838782</v>
+        <v>-1.081096364838777</v>
       </c>
       <c r="F85">
-        <v>-1.30067565884078</v>
+        <v>-1.300675658840784</v>
       </c>
       <c r="G85">
-        <v>-0.1083394007793171</v>
+        <v>-0.1083394007793157</v>
       </c>
     </row>
     <row r="86">
@@ -2674,16 +2674,16 @@
         <v>1.488776759943977</v>
       </c>
       <c r="D86">
-        <v>0.1896127478065059</v>
+        <v>0.1896127478065062</v>
       </c>
       <c r="E86">
-        <v>0.09169334301828468</v>
+        <v>0.09169334301828397</v>
       </c>
       <c r="F86">
-        <v>0.1986250683850736</v>
+        <v>0.198625068385074</v>
       </c>
       <c r="G86">
-        <v>0.8102607781994829</v>
+        <v>0.8102607781994824</v>
       </c>
     </row>
     <row r="87">
@@ -2698,19 +2698,19 @@
         </is>
       </c>
       <c r="C87">
-        <v>0.3794623340781712</v>
+        <v>0.3794623340781728</v>
       </c>
       <c r="D87">
-        <v>-0.650621406164163</v>
+        <v>-0.6506214061641642</v>
       </c>
       <c r="E87">
         <v>1.246182561425931</v>
       </c>
       <c r="F87">
-        <v>-0.093489094596762</v>
+        <v>-0.09348909459675925</v>
       </c>
       <c r="G87">
-        <v>-0.826739083764837</v>
+        <v>-0.8267390837648384</v>
       </c>
     </row>
     <row r="88">
@@ -2725,19 +2725,19 @@
         </is>
       </c>
       <c r="C88">
-        <v>2.112726340202557</v>
+        <v>2.112726340202556</v>
       </c>
       <c r="D88">
-        <v>1.45443401300085</v>
+        <v>1.454434013000851</v>
       </c>
       <c r="E88">
-        <v>0.3938519187989186</v>
+        <v>0.3938519187989192</v>
       </c>
       <c r="F88">
-        <v>0.2065873768708529</v>
+        <v>0.2065873768708535</v>
       </c>
       <c r="G88">
-        <v>-0.06770424623215772</v>
+        <v>-0.06770424623215729</v>
       </c>
     </row>
     <row r="89">
@@ -2752,19 +2752,19 @@
         </is>
       </c>
       <c r="C89">
-        <v>0.4565945746640265</v>
+        <v>0.4565945746640263</v>
       </c>
       <c r="D89">
-        <v>-0.1466378345778503</v>
+        <v>-0.1466378345778493</v>
       </c>
       <c r="E89">
-        <v>-0.4977788315274514</v>
+        <v>-0.4977788315274517</v>
       </c>
       <c r="F89">
-        <v>-0.004447644007439426</v>
+        <v>-0.004447644007440521</v>
       </c>
       <c r="G89">
-        <v>-0.08244606622555245</v>
+        <v>-0.08244606622555277</v>
       </c>
     </row>
     <row r="90">
@@ -2782,16 +2782,16 @@
         <v>-2.201573546933335</v>
       </c>
       <c r="D90">
-        <v>-2.015802002020863</v>
+        <v>-2.015802002020861</v>
       </c>
       <c r="E90">
-        <v>-2.615924584378313</v>
+        <v>-2.615924584378314</v>
       </c>
       <c r="F90">
-        <v>-0.3215036323545007</v>
+        <v>-0.3215036323545071</v>
       </c>
       <c r="G90">
-        <v>0.07467349307280115</v>
+        <v>0.07467349307280041</v>
       </c>
     </row>
     <row r="91">
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="C91">
-        <v>0.8796869179911853</v>
+        <v>0.8796869179911856</v>
       </c>
       <c r="D91">
-        <v>0.2116284612324839</v>
+        <v>0.2116284612324833</v>
       </c>
       <c r="E91">
         <v>0.4094075813468577</v>
       </c>
       <c r="F91">
-        <v>0.1401968341412918</v>
+        <v>0.1401968341412928</v>
       </c>
       <c r="G91">
-        <v>1.008990028410121</v>
+        <v>1.00899002841012</v>
       </c>
     </row>
     <row r="92">
@@ -2833,19 +2833,19 @@
         </is>
       </c>
       <c r="C92">
-        <v>0.9190608593394087</v>
+        <v>0.9190608593394102</v>
       </c>
       <c r="D92">
-        <v>-0.6363935130559346</v>
+        <v>-0.6363935130559351</v>
       </c>
       <c r="E92">
-        <v>0.6579454164510045</v>
+        <v>0.657945416451003</v>
       </c>
       <c r="F92">
-        <v>0.03218162553174745</v>
+        <v>0.03218162553174919</v>
       </c>
       <c r="G92">
-        <v>-0.1299497027863028</v>
+        <v>-0.1299497027863039</v>
       </c>
     </row>
     <row r="93">
@@ -2860,19 +2860,19 @@
         </is>
       </c>
       <c r="C93">
-        <v>0.2377779310362052</v>
+        <v>0.2377779310362061</v>
       </c>
       <c r="D93">
-        <v>-0.2501910075410428</v>
+        <v>-0.2501910075410432</v>
       </c>
       <c r="E93">
-        <v>0.4479725293902049</v>
+        <v>0.4479725293902064</v>
       </c>
       <c r="F93">
-        <v>-0.619460529488297</v>
+        <v>-0.6194605294882964</v>
       </c>
       <c r="G93">
-        <v>-0.6552526267286423</v>
+        <v>-0.6552526267286427</v>
       </c>
     </row>
     <row r="94">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="C94">
-        <v>0.8867136301444465</v>
+        <v>0.8867136301444477</v>
       </c>
       <c r="D94">
-        <v>-0.5687133490666157</v>
+        <v>-0.5687133490666163</v>
       </c>
       <c r="E94">
-        <v>0.40227368472016</v>
+        <v>0.4022736847201588</v>
       </c>
       <c r="F94">
-        <v>0.09534682368698424</v>
+        <v>0.09534682368698555</v>
       </c>
       <c r="G94">
-        <v>0.6362716873385478</v>
+        <v>0.6362716873385467</v>
       </c>
     </row>
     <row r="95">
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C95">
-        <v>-4.80520238272197</v>
+        <v>-4.805202382721977</v>
       </c>
       <c r="D95">
-        <v>2.556216918684427</v>
+        <v>2.556216918684425</v>
       </c>
       <c r="E95">
-        <v>-0.2009648063083679</v>
+        <v>-0.2009648063083656</v>
       </c>
       <c r="F95">
-        <v>1.114100772324407</v>
+        <v>1.114100772324405</v>
       </c>
       <c r="G95">
-        <v>-0.01657779384273636</v>
+        <v>-0.01657779384273561</v>
       </c>
     </row>
     <row r="96">
@@ -2941,19 +2941,19 @@
         </is>
       </c>
       <c r="C96">
-        <v>0.8163556142143724</v>
+        <v>0.8163556142143742</v>
       </c>
       <c r="D96">
-        <v>-0.9630237189587801</v>
+        <v>-0.9630237189587807</v>
       </c>
       <c r="E96">
-        <v>0.6909057825611876</v>
+        <v>0.690905782561186</v>
       </c>
       <c r="F96">
-        <v>0.007167697458267984</v>
+        <v>0.007167697458269839</v>
       </c>
       <c r="G96">
-        <v>-0.2087708200934209</v>
+        <v>-0.2087708200934223</v>
       </c>
     </row>
     <row r="97">
@@ -2968,16 +2968,16 @@
         </is>
       </c>
       <c r="C97">
-        <v>0.6329588070795723</v>
+        <v>0.6329588070795711</v>
       </c>
       <c r="D97">
-        <v>0.2425405501935279</v>
+        <v>0.2425405501935294</v>
       </c>
       <c r="E97">
-        <v>-1.024603850059763</v>
+        <v>-1.024603850059764</v>
       </c>
       <c r="F97">
-        <v>0.2286714600221733</v>
+        <v>0.2286714600221711</v>
       </c>
       <c r="G97">
         <v>0.4428006021858943</v>
@@ -2995,19 +2995,19 @@
         </is>
       </c>
       <c r="C98">
-        <v>-1.93992287932686</v>
+        <v>-1.939922879326863</v>
       </c>
       <c r="D98">
-        <v>1.016086173292045</v>
+        <v>1.016086173292044</v>
       </c>
       <c r="E98">
-        <v>0.007185470983218909</v>
+        <v>0.007185470983220754</v>
       </c>
       <c r="F98">
-        <v>0.1090574881834091</v>
+        <v>0.1090574881834082</v>
       </c>
       <c r="G98">
-        <v>0.1126160808435615</v>
+        <v>0.1126160808435614</v>
       </c>
     </row>
     <row r="99">
@@ -3022,19 +3022,19 @@
         </is>
       </c>
       <c r="C99">
-        <v>1.114671309641605</v>
+        <v>1.114671309641606</v>
       </c>
       <c r="D99">
-        <v>-0.1091642367888324</v>
+        <v>-0.1091642367888326</v>
       </c>
       <c r="E99">
-        <v>0.3612480841933577</v>
+        <v>0.361248084193357</v>
       </c>
       <c r="F99">
-        <v>0.1266111514272818</v>
+        <v>0.1266111514272827</v>
       </c>
       <c r="G99">
-        <v>0.5691764399123767</v>
+        <v>0.5691764399123759</v>
       </c>
     </row>
     <row r="100">
@@ -3049,19 +3049,19 @@
         </is>
       </c>
       <c r="C100">
-        <v>0.6013409250547322</v>
+        <v>0.6013409250547332</v>
       </c>
       <c r="D100">
-        <v>-0.5629265883456831</v>
+        <v>-0.5629265883456828</v>
       </c>
       <c r="E100">
-        <v>-0.4940069342359475</v>
+        <v>-0.4940069342359465</v>
       </c>
       <c r="F100">
-        <v>-0.6197834396511762</v>
+        <v>-0.6197834396511773</v>
       </c>
       <c r="G100">
-        <v>0.4353594464558014</v>
+        <v>0.4353594464558012</v>
       </c>
     </row>
     <row r="101">
@@ -3082,13 +3082,13 @@
         <v>0.994191132558214</v>
       </c>
       <c r="E101">
-        <v>0.525184650144645</v>
+        <v>0.5251846501446453</v>
       </c>
       <c r="F101">
-        <v>0.1511854854112979</v>
+        <v>0.1511854854112988</v>
       </c>
       <c r="G101">
-        <v>0.1747880777465084</v>
+        <v>0.1747880777465085</v>
       </c>
     </row>
     <row r="102">
@@ -3106,16 +3106,16 @@
         <v>1.382183013602582</v>
       </c>
       <c r="D102">
-        <v>0.6503563955485403</v>
+        <v>0.6503563955485404</v>
       </c>
       <c r="E102">
-        <v>0.3631490046828518</v>
+        <v>0.363149004682852</v>
       </c>
       <c r="F102">
-        <v>0.1735395824035058</v>
+        <v>0.1735395824035066</v>
       </c>
       <c r="G102">
-        <v>0.6715664065815364</v>
+        <v>0.671566406581536</v>
       </c>
     </row>
     <row r="103">
@@ -3130,19 +3130,19 @@
         </is>
       </c>
       <c r="C103">
-        <v>-0.05551262729997467</v>
+        <v>-0.05551262729997269</v>
       </c>
       <c r="D103">
-        <v>-1.190136728870688</v>
+        <v>-1.190136728870689</v>
       </c>
       <c r="E103">
-        <v>0.159886372582963</v>
+        <v>0.159886372582964</v>
       </c>
       <c r="F103">
-        <v>-0.6713112802322941</v>
+        <v>-0.6713112802322938</v>
       </c>
       <c r="G103">
-        <v>0.07103382097032936</v>
+        <v>0.07103382097032843</v>
       </c>
     </row>
     <row r="104">
@@ -3157,19 +3157,19 @@
         </is>
       </c>
       <c r="C104">
-        <v>0.6981893987997404</v>
+        <v>0.6981893987997421</v>
       </c>
       <c r="D104">
-        <v>-0.906570356282034</v>
+        <v>-0.9065703562820346</v>
       </c>
       <c r="E104">
-        <v>0.6811897736918846</v>
+        <v>0.681189773691883</v>
       </c>
       <c r="F104">
-        <v>0.01320208630922685</v>
+        <v>0.0132020863092287</v>
       </c>
       <c r="G104">
-        <v>-0.004566828192750301</v>
+        <v>-0.004566828192751698</v>
       </c>
     </row>
     <row r="105">
@@ -3184,19 +3184,19 @@
         </is>
       </c>
       <c r="C105">
-        <v>1.253597793979169</v>
+        <v>1.253597793979166</v>
       </c>
       <c r="D105">
-        <v>1.254630142657448</v>
+        <v>1.25463014265745</v>
       </c>
       <c r="E105">
-        <v>-0.2378190529489792</v>
+        <v>-0.2378190529489818</v>
       </c>
       <c r="F105">
         <v>1.241012480595076</v>
       </c>
       <c r="G105">
-        <v>-0.06229770992238093</v>
+        <v>-0.06229770992238114</v>
       </c>
     </row>
     <row r="106">
@@ -3211,19 +3211,19 @@
         </is>
       </c>
       <c r="C106">
-        <v>-1.365941567356397</v>
+        <v>-1.365941567356396</v>
       </c>
       <c r="D106">
-        <v>-1.467986258134593</v>
+        <v>-1.467986258134596</v>
       </c>
       <c r="E106">
-        <v>0.7862002636690819</v>
+        <v>0.7862002636690796</v>
       </c>
       <c r="F106">
-        <v>0.5780681332753731</v>
+        <v>0.5780681332753753</v>
       </c>
       <c r="G106">
-        <v>1.031206552286089</v>
+        <v>1.031206552286087</v>
       </c>
     </row>
     <row r="107">
@@ -3238,19 +3238,19 @@
         </is>
       </c>
       <c r="C107">
-        <v>-0.8462520126977569</v>
+        <v>-0.8462520126977563</v>
       </c>
       <c r="D107">
-        <v>-1.354644362673932</v>
+        <v>-1.354644362673931</v>
       </c>
       <c r="E107">
-        <v>-0.9337125872700005</v>
+        <v>-0.9337125872700012</v>
       </c>
       <c r="F107">
-        <v>-0.3444774459416438</v>
+        <v>-0.344477445941646</v>
       </c>
       <c r="G107">
-        <v>-0.346836331312768</v>
+        <v>-0.3468363313127688</v>
       </c>
     </row>
     <row r="108">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C108">
-        <v>0.3767388615902544</v>
+        <v>0.376738861590254</v>
       </c>
       <c r="D108">
-        <v>0.03245795230994095</v>
+        <v>0.0324579523099418</v>
       </c>
       <c r="E108">
-        <v>0.0578394179063739</v>
+        <v>0.05783941790637305</v>
       </c>
       <c r="F108">
-        <v>0.2401732978473543</v>
+        <v>0.2401732978473544</v>
       </c>
       <c r="G108">
-        <v>-0.655849824050274</v>
+        <v>-0.6558498240502746</v>
       </c>
     </row>
     <row r="109">
@@ -3292,19 +3292,19 @@
         </is>
       </c>
       <c r="C109">
-        <v>0.1304793444435845</v>
+        <v>0.1304793444435837</v>
       </c>
       <c r="D109">
-        <v>0.1848170186350732</v>
+        <v>0.1848170186350733</v>
       </c>
       <c r="E109">
-        <v>0.2248999454116351</v>
+        <v>0.2248999454116328</v>
       </c>
       <c r="F109">
-        <v>0.9938455440178019</v>
+        <v>0.9938455440178029</v>
       </c>
       <c r="G109">
-        <v>0.3991844734858367</v>
+        <v>0.3991844734858357</v>
       </c>
     </row>
     <row r="110">
@@ -3322,16 +3322,16 @@
         <v>-1.643007525402362</v>
       </c>
       <c r="D110">
-        <v>-1.441471154213633</v>
+        <v>-1.441471154213634</v>
       </c>
       <c r="E110">
-        <v>0.881749011271337</v>
+        <v>0.8817490112713318</v>
       </c>
       <c r="F110">
-        <v>1.088635089699896</v>
+        <v>1.088635089699899</v>
       </c>
       <c r="G110">
-        <v>-1.002649732056967</v>
+        <v>-1.002649732056969</v>
       </c>
     </row>
     <row r="111">
@@ -3346,16 +3346,16 @@
         </is>
       </c>
       <c r="C111">
-        <v>-0.661875782832352</v>
+        <v>-0.6618757828323529</v>
       </c>
       <c r="D111">
-        <v>-0.4026413527347096</v>
+        <v>-0.4026413527347082</v>
       </c>
       <c r="E111">
-        <v>-1.820867290170191</v>
+        <v>-1.82086729017019</v>
       </c>
       <c r="F111">
-        <v>-0.3942419948507239</v>
+        <v>-0.3942419948507284</v>
       </c>
       <c r="G111">
         <v>1.016662727654405</v>
@@ -3373,19 +3373,19 @@
         </is>
       </c>
       <c r="C112">
-        <v>1.143310039914772</v>
+        <v>1.143310039914773</v>
       </c>
       <c r="D112">
-        <v>-0.06613554810382755</v>
+        <v>-0.06613554810382763</v>
       </c>
       <c r="E112">
-        <v>0.5937705941573319</v>
+        <v>0.5937705941573312</v>
       </c>
       <c r="F112">
-        <v>0.07957889615190331</v>
+        <v>0.07957889615190472</v>
       </c>
       <c r="G112">
-        <v>0.02515787704116189</v>
+        <v>0.0251578770411611</v>
       </c>
     </row>
     <row r="113">
@@ -3400,19 +3400,19 @@
         </is>
       </c>
       <c r="C113">
-        <v>-0.06757181232499007</v>
+        <v>-0.0675718123249901</v>
       </c>
       <c r="D113">
-        <v>0.03683407227569929</v>
+        <v>0.03683407227569956</v>
       </c>
       <c r="E113">
-        <v>-1.101059191573159</v>
+        <v>-1.101059191573155</v>
       </c>
       <c r="F113">
-        <v>-1.254648325370922</v>
+        <v>-1.254648325370925</v>
       </c>
       <c r="G113">
-        <v>0.7707833845265044</v>
+        <v>0.7707833845265052</v>
       </c>
     </row>
     <row r="114">
@@ -3427,19 +3427,19 @@
         </is>
       </c>
       <c r="C114">
-        <v>-3.36162883027852</v>
+        <v>-3.361628830278522</v>
       </c>
       <c r="D114">
-        <v>1.249181615254778</v>
+        <v>1.249181615254775</v>
       </c>
       <c r="E114">
-        <v>0.5166183022027625</v>
+        <v>0.5166183022027673</v>
       </c>
       <c r="F114">
-        <v>-0.2782976879006163</v>
+        <v>-0.2782976879006166</v>
       </c>
       <c r="G114">
-        <v>0.969506536768437</v>
+        <v>0.9695065367684369</v>
       </c>
     </row>
     <row r="115">
@@ -3454,19 +3454,19 @@
         </is>
       </c>
       <c r="C115">
-        <v>-3.033082965462615</v>
+        <v>-3.033082965462612</v>
       </c>
       <c r="D115">
-        <v>-3.101644855597494</v>
+        <v>-3.101644855597496</v>
       </c>
       <c r="E115">
-        <v>0.3809774222698636</v>
+        <v>0.3809774222698622</v>
       </c>
       <c r="F115">
-        <v>-0.1180727756328847</v>
+        <v>-0.1180727756328834</v>
       </c>
       <c r="G115">
-        <v>0.7492873497107483</v>
+        <v>0.749287349710746</v>
       </c>
     </row>
     <row r="116">
@@ -3481,19 +3481,19 @@
         </is>
       </c>
       <c r="C116">
-        <v>0.7492685148497693</v>
+        <v>0.7492685148497714</v>
       </c>
       <c r="D116">
         <v>-1.080164485336503</v>
       </c>
       <c r="E116">
-        <v>1.153945330276644</v>
+        <v>1.153945330276642</v>
       </c>
       <c r="F116">
-        <v>-0.09903343794720212</v>
+        <v>-0.09903343794719932</v>
       </c>
       <c r="G116">
-        <v>-1.255905920183962</v>
+        <v>-1.255905920183964</v>
       </c>
     </row>
     <row r="117">
@@ -3508,19 +3508,19 @@
         </is>
       </c>
       <c r="C117">
-        <v>-0.92933564133869</v>
+        <v>-0.9293356413386892</v>
       </c>
       <c r="D117">
         <v>-1.848430926394386</v>
       </c>
       <c r="E117">
-        <v>-0.9118777989207371</v>
+        <v>-0.9118777989207389</v>
       </c>
       <c r="F117">
-        <v>-0.0706362755249797</v>
+        <v>-0.07063627552498147</v>
       </c>
       <c r="G117">
-        <v>0.08991683804963103</v>
+        <v>0.08991683804962999</v>
       </c>
     </row>
     <row r="118">
@@ -3535,19 +3535,19 @@
         </is>
       </c>
       <c r="C118">
-        <v>0.8983387054901404</v>
+        <v>0.8983387054901401</v>
       </c>
       <c r="D118">
-        <v>0.8636987328953154</v>
+        <v>0.8636987328953161</v>
       </c>
       <c r="E118">
-        <v>-0.1967634029527635</v>
+        <v>-0.1967634029527606</v>
       </c>
       <c r="F118">
-        <v>-0.6577265270990105</v>
+        <v>-0.6577265270990116</v>
       </c>
       <c r="G118">
-        <v>-0.1397516878953833</v>
+        <v>-0.1397516878953825</v>
       </c>
     </row>
     <row r="119">
@@ -3562,19 +3562,19 @@
         </is>
       </c>
       <c r="C119">
-        <v>0.819358140534073</v>
+        <v>0.8193581405340741</v>
       </c>
       <c r="D119">
-        <v>-0.2107233866229539</v>
+        <v>-0.2107233866229542</v>
       </c>
       <c r="E119">
         <v>1.194713219566338</v>
       </c>
       <c r="F119">
-        <v>-0.0567848845641837</v>
+        <v>-0.05678488456418113</v>
       </c>
       <c r="G119">
-        <v>-1.025200041407435</v>
+        <v>-1.025200041407436</v>
       </c>
     </row>
     <row r="120">
@@ -3592,16 +3592,16 @@
         <v>1.356417075502778</v>
       </c>
       <c r="D120">
-        <v>0.6244708648954852</v>
+        <v>0.624470864895485</v>
       </c>
       <c r="E120">
-        <v>0.3485276466377214</v>
+        <v>0.3485276466377217</v>
       </c>
       <c r="F120">
-        <v>0.1769625823669038</v>
+        <v>0.1769625823669045</v>
       </c>
       <c r="G120">
-        <v>0.7671118105906505</v>
+        <v>0.7671118105906501</v>
       </c>
     </row>
     <row r="121">
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C121">
-        <v>-2.004132018742005</v>
+        <v>-2.004132018742003</v>
       </c>
       <c r="D121">
-        <v>-0.03078004446585662</v>
+        <v>-0.03078004446586084</v>
       </c>
       <c r="E121">
-        <v>2.610202462767755</v>
+        <v>2.61020246276776</v>
       </c>
       <c r="F121">
-        <v>-0.2647040736305888</v>
+        <v>-0.2647040736305834</v>
       </c>
       <c r="G121">
-        <v>1.171999772015025</v>
+        <v>1.171999772015023</v>
       </c>
     </row>
     <row r="122">
@@ -3643,19 +3643,19 @@
         </is>
       </c>
       <c r="C122">
-        <v>-0.1232902566678298</v>
+        <v>-0.1232902566678316</v>
       </c>
       <c r="D122">
-        <v>0.6577080857308645</v>
+        <v>0.6577080857308667</v>
       </c>
       <c r="E122">
-        <v>-1.373500996548703</v>
+        <v>-1.373500996548701</v>
       </c>
       <c r="F122">
-        <v>-0.6085592579668047</v>
+        <v>-0.6085592579668087</v>
       </c>
       <c r="G122">
-        <v>-0.9720876455968451</v>
+        <v>-0.9720876455968442</v>
       </c>
     </row>
     <row r="123">
@@ -3670,16 +3670,16 @@
         </is>
       </c>
       <c r="C123">
-        <v>0.3991030480194828</v>
+        <v>0.3991030480194842</v>
       </c>
       <c r="D123">
-        <v>-0.6585278087937827</v>
+        <v>-0.6585278087937821</v>
       </c>
       <c r="E123">
-        <v>-0.06577274865633785</v>
+        <v>-0.06577274865633559</v>
       </c>
       <c r="F123">
-        <v>-1.032399206161615</v>
+        <v>-1.032399206161616</v>
       </c>
       <c r="G123">
         <v>-1.131884116927919</v>
@@ -3697,19 +3697,19 @@
         </is>
       </c>
       <c r="C124">
-        <v>-0.2925879959887325</v>
+        <v>-0.2925879959887312</v>
       </c>
       <c r="D124">
-        <v>-0.7589349085329093</v>
+        <v>-0.7589349085329099</v>
       </c>
       <c r="E124">
-        <v>0.02047988744371194</v>
+        <v>0.02047988744371443</v>
       </c>
       <c r="F124">
-        <v>-0.9031643984957111</v>
+        <v>-0.9031643984957114</v>
       </c>
       <c r="G124">
-        <v>0.06235524853118866</v>
+        <v>0.06235524853118807</v>
       </c>
     </row>
     <row r="125">
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c r="C125">
-        <v>-1.890929971837679</v>
+        <v>-1.890929971837681</v>
       </c>
       <c r="D125">
-        <v>0.07805139491662437</v>
+        <v>0.07805139491662477</v>
       </c>
       <c r="E125">
-        <v>0.3056463952082252</v>
+        <v>0.3056463952082226</v>
       </c>
       <c r="F125">
-        <v>0.8859385454174133</v>
+        <v>0.8859385454174136</v>
       </c>
       <c r="G125">
-        <v>-2.312780049496055</v>
+        <v>-2.312780049496056</v>
       </c>
     </row>
     <row r="126">
@@ -3751,19 +3751,19 @@
         </is>
       </c>
       <c r="C126">
-        <v>-2.151381002367017</v>
+        <v>-2.151381002367018</v>
       </c>
       <c r="D126">
         <v>-1.454331787745224</v>
       </c>
       <c r="E126">
-        <v>-0.47507628919824</v>
+        <v>-0.4750762891982439</v>
       </c>
       <c r="F126">
-        <v>0.9126553557578263</v>
+        <v>0.9126553557578254</v>
       </c>
       <c r="G126">
-        <v>0.1132732313839834</v>
+        <v>0.1132732313839814</v>
       </c>
     </row>
   </sheetData>
